--- a/data/trans_dic/Q20C_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 86,52</t>
+          <t>12,26; 85,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,18</t>
+          <t>0,0; 82,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,34; 54,73</t>
+          <t>10,58; 60,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,5</t>
+          <t>0,0; 87,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,82</t>
+          <t>0,0; 68,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 68,5</t>
+          <t>8,73; 68,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,87; 73,29</t>
+          <t>13,94; 72,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 52,32</t>
+          <t>11,06; 53,71</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,54</t>
+          <t>0,0; 69,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,3</t>
+          <t>0,0; 40,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,9</t>
+          <t>0,0; 84,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 61,95</t>
+          <t>8,27; 63,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,52</t>
+          <t>0,0; 27,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,64</t>
+          <t>0,0; 71,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 52,99</t>
+          <t>6,2; 55,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,88</t>
+          <t>0,0; 54,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,91; 56,19</t>
+          <t>10,35; 54,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 83,92</t>
+          <t>14,59; 83,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,42</t>
+          <t>0,0; 78,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 75,59</t>
+          <t>11,56; 83,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,05</t>
+          <t>0,0; 50,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,87; 56,88</t>
+          <t>13,61; 53,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 44,63</t>
+          <t>4,75; 44,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,44; 56,28</t>
+          <t>15,36; 53,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,98</t>
+          <t>0,0; 46,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,74</t>
+          <t>0,0; 22,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 56,93</t>
+          <t>11,62; 60,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,24</t>
+          <t>0,0; 48,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 62,56</t>
+          <t>7,62; 56,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 56,84</t>
+          <t>6,76; 56,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 62,57</t>
+          <t>8,62; 65,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 51,78</t>
+          <t>5,94; 52,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 42,27</t>
+          <t>10,94; 41,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 29,82</t>
+          <t>5,63; 29,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 51,49</t>
+          <t>16,03; 51,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 38,79</t>
+          <t>6,4; 37,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,26</t>
+          <t>0,0; 81,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 58,37</t>
+          <t>7,4; 56,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,49; 75,46</t>
+          <t>18,86; 77,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,81; 41,84</t>
+          <t>7,9; 40,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,51; 66,88</t>
+          <t>18,14; 66,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 40,14</t>
+          <t>6,5; 38,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,53</t>
+          <t>0,0; 39,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 40,07</t>
+          <t>12,25; 40,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,89; 52,76</t>
+          <t>12,27; 48,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 49,69</t>
+          <t>17,9; 50,2</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,43; 49,05</t>
+          <t>10,58; 52,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,5; 38,21</t>
+          <t>2,79; 35,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,94</t>
+          <t>0,0; 44,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,3</t>
+          <t>0,0; 33,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,11; 47,72</t>
+          <t>10,2; 47,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 38,96</t>
+          <t>4,42; 38,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,98; 49,78</t>
+          <t>5,32; 48,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,7</t>
+          <t>0,0; 50,3</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,05; 43,79</t>
+          <t>13,46; 42,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,37; 30,79</t>
+          <t>10,33; 31,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,87; 38,72</t>
+          <t>11,27; 35,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,12; 40,07</t>
+          <t>16,52; 38,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,14; 30,04</t>
+          <t>9,32; 30,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,96; 37,77</t>
+          <t>17,77; 37,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,52; 39,48</t>
+          <t>15,44; 38,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,71; 29,39</t>
+          <t>11,36; 29,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,61; 30,44</t>
+          <t>13,58; 31,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,01; 32,48</t>
+          <t>17,14; 31,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,72; 33,58</t>
+          <t>17,33; 34,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,15; 30,93</t>
+          <t>16,52; 31,63</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>903; 6337</t>
+          <t>898; 6276</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4993</t>
+          <t>0; 4995</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1771</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1247; 7310</t>
+          <t>1413; 8015</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1274</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6359</t>
+          <t>0; 6507</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1413</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1634</t>
+          <t>0; 1710</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>888; 6982</t>
+          <t>890; 6984</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1874; 9904</t>
+          <t>1884; 9842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1881</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1678; 8287</t>
+          <t>1752; 8506</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1094</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 980</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1164</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1472</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2165,32 +2165,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5064</t>
+          <t>0; 5780</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3055</t>
+          <t>0; 3245</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1580</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 5169</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942; 7664</t>
+          <t>1023; 7817</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4011</t>
+          <t>0; 3802</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4685</t>
+          <t>0; 4661</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>966; 7855</t>
+          <t>919; 8168</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5531</t>
+          <t>0; 5924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1193; 7519</t>
+          <t>1384; 7306</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1245</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>935; 5319</t>
+          <t>925; 5306</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4426</t>
+          <t>0; 4358</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>484; 3305</t>
+          <t>505; 3647</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4770</t>
+          <t>0; 4730</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2935; 12037</t>
+          <t>2880; 11356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>792; 7339</t>
+          <t>782; 7360</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2741; 9991</t>
+          <t>2726; 9524</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5339</t>
+          <t>0; 5598</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5807</t>
+          <t>0; 4909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2170; 10606</t>
+          <t>2166; 11305</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5895</t>
+          <t>0; 6364</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>971; 7394</t>
+          <t>901; 6658</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1035; 8556</t>
+          <t>1018; 8534</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1024; 7919</t>
+          <t>1091; 8231</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>527; 4606</t>
+          <t>529; 4701</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1990; 10128</t>
+          <t>2621; 10018</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2031; 10967</t>
+          <t>2071; 10952</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5214; 16112</t>
+          <t>5016; 16068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1471; 8505</t>
+          <t>1404; 8241</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3616</t>
+          <t>0; 3655</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1007; 7789</t>
+          <t>987; 7542</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1691</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2003; 8174</t>
+          <t>2043; 8345</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1665</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2177; 11664</t>
+          <t>2204; 11390</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2919; 11144</t>
+          <t>3023; 11160</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>889; 5144</t>
+          <t>834; 4987</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5427</t>
+          <t>0; 5322</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5078; 16515</t>
+          <t>5049; 16585</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3694; 13090</t>
+          <t>3045; 12091</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4060; 11750</t>
+          <t>4234; 11872</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 680</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2977,52 +2977,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>249; 1088</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>119; 521</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1937; 9110</t>
+          <t>1964; 9824</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>902; 7665</t>
+          <t>559; 7187</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5939</t>
+          <t>0; 6474</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1605</t>
+          <t>0; 1838</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1967; 9285</t>
+          <t>1985; 9149</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>991; 8633</t>
+          <t>979; 8629</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>932; 7764</t>
+          <t>829; 7583</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 2561</t>
+          <t>0; 3017</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4680; 14587</t>
+          <t>4484; 14136</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5604; 18409</t>
+          <t>6173; 18557</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6087; 19857</t>
+          <t>5778; 18392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9714; 22730</t>
+          <t>9372; 21865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3990; 14723</t>
+          <t>4570; 14833</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14580; 30653</t>
+          <t>14419; 30731</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9952; 23784</t>
+          <t>9300; 23282</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4499; 12351</t>
+          <t>4774; 12445</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11208; 25061</t>
+          <t>11181; 26193</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23978; 45776</t>
+          <t>24158; 44475</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18642; 37453</t>
+          <t>19332; 38315</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15953; 30547</t>
+          <t>16318; 31240</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q20C_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,26; 85,68</t>
+          <t>12,64; 87,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,21</t>
+          <t>0,0; 82,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 60,0</t>
+          <t>9,67; 56,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,49</t>
+          <t>0,0; 86,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,88</t>
+          <t>0,0; 80,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 68,52</t>
+          <t>8,91; 74,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,94; 72,83</t>
+          <t>15,2; 74,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 53,71</t>
+          <t>10,43; 50,87</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,1</t>
+          <t>0,0; 60,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,67</t>
+          <t>0,0; 29,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,49</t>
+          <t>0,0; 84,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 63,18</t>
+          <t>8,04; 65,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,98</t>
+          <t>0,0; 22,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,27</t>
+          <t>0,0; 71,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 55,11</t>
+          <t>6,13; 49,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,5</t>
+          <t>0,0; 48,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 54,6</t>
+          <t>17,25; 65,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,59; 83,72</t>
+          <t>15,2; 83,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,2</t>
+          <t>0,0; 79,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 83,42</t>
+          <t>9,59; 84,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,62</t>
+          <t>0,0; 60,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,61; 53,67</t>
+          <t>13,38; 54,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 44,76</t>
+          <t>5,88; 45,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,36; 53,64</t>
+          <t>19,34; 62,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,12</t>
+          <t>0,0; 42,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,6</t>
+          <t>0,0; 25,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,62; 60,68</t>
+          <t>11,92; 60,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,83</t>
+          <t>0,0; 43,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 56,33</t>
+          <t>8,18; 61,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 56,69</t>
+          <t>8,4; 57,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 65,03</t>
+          <t>7,93; 61,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 52,85</t>
+          <t>5,39; 47,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 41,81</t>
+          <t>8,92; 40,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 29,78</t>
+          <t>5,72; 29,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,03; 51,35</t>
+          <t>14,49; 50,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 37,59</t>
+          <t>5,3; 34,77</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,14</t>
+          <t>0,0; 80,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 56,52</t>
+          <t>7,48; 55,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,86; 77,05</t>
+          <t>17,38; 72,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,44 +1302,44 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 40,86</t>
+          <t>7,77; 42,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,14; 66,97</t>
+          <t>22,0; 68,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 38,91</t>
+          <t>11,3; 45,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,74</t>
+          <t>0,0; 39,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 40,23</t>
+          <t>11,21; 39,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,27; 48,73</t>
+          <t>12,57; 50,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,9; 50,2</t>
+          <t>19,0; 52,06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,58; 52,89</t>
+          <t>10,29; 49,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,79; 35,83</t>
+          <t>4,44; 37,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,63</t>
+          <t>0,0; 39,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,55</t>
+          <t>0,0; 30,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,2; 47,02</t>
+          <t>9,97; 50,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 38,94</t>
+          <t>4,78; 40,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 48,63</t>
+          <t>5,86; 51,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,3</t>
+          <t>0,0; 48,56</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,46; 42,44</t>
+          <t>13,49; 44,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,33; 31,04</t>
+          <t>10,52; 32,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,27; 35,87</t>
+          <t>11,01; 35,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,52; 38,54</t>
+          <t>18,9; 40,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,32; 30,26</t>
+          <t>8,32; 30,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,77; 37,86</t>
+          <t>17,42; 37,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,44; 38,64</t>
+          <t>16,25; 39,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,36; 29,62</t>
+          <t>11,91; 30,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,58; 31,82</t>
+          <t>13,24; 31,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,14; 31,56</t>
+          <t>16,95; 31,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,33; 34,35</t>
+          <t>17,23; 33,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,52; 31,63</t>
+          <t>18,02; 33,2</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4809</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>898; 6276</t>
+          <t>926; 6373</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4995</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1413; 8015</t>
+          <t>1346; 7859</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6507</t>
+          <t>0; 6410</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>0; 2442</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>890; 6984</t>
+          <t>908; 7618</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1884; 9842</t>
+          <t>2054; 10086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1752; 8506</t>
+          <t>1769; 8630</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>590</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>590</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5780</t>
+          <t>0; 5066</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3245</t>
+          <t>0; 2859</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5169</t>
+          <t>0; 5157</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1023; 7817</t>
+          <t>994; 8068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3802</t>
+          <t>0; 3601</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>8705</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4661</t>
+          <t>0; 4678</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>919; 8168</t>
+          <t>909; 7282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5924</t>
+          <t>0; 5294</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1384; 7306</t>
+          <t>2886; 11038</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,37 +2368,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>925; 5306</t>
+          <t>963; 5316</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4358</t>
+          <t>0; 4423</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>505; 3647</t>
+          <t>452; 4002</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4730</t>
+          <t>0; 5676</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2880; 11356</t>
+          <t>2831; 11629</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>782; 7360</t>
+          <t>967; 7556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2726; 9524</t>
+          <t>4146; 13474</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3816</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5598</t>
+          <t>0; 5170</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4909</t>
+          <t>0; 5439</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2166; 11305</t>
+          <t>2220; 11333</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6364</t>
+          <t>0; 5699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>901; 6658</t>
+          <t>967; 7295</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1018; 8534</t>
+          <t>1264; 8729</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1091; 8231</t>
+          <t>1004; 7749</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>529; 4701</t>
+          <t>567; 4956</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2621; 10018</t>
+          <t>2137; 9637</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2071; 10952</t>
+          <t>2102; 10888</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5016; 16068</t>
+          <t>4535; 15826</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1404; 8241</t>
+          <t>1255; 8241</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>8803</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3655</t>
+          <t>0; 3616</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>987; 7542</t>
+          <t>998; 7466</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2043; 8345</t>
+          <t>2040; 8450</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2784,44 +2784,44 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2204; 11390</t>
+          <t>2165; 11757</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3023; 11160</t>
+          <t>3666; 11399</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>834; 4987</t>
+          <t>1680; 6795</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5322</t>
+          <t>0; 5289</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5049; 16585</t>
+          <t>4620; 16109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3045; 12091</t>
+          <t>3120; 12569</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4234; 11872</t>
+          <t>5052; 13845</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>349</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>856</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1964; 9824</t>
+          <t>1911; 9134</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>559; 7187</t>
+          <t>891; 7454</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6474</t>
+          <t>0; 5710</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1838</t>
+          <t>0; 1771</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1985; 9149</t>
+          <t>1940; 9872</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>979; 8629</t>
+          <t>1059; 8979</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>829; 7583</t>
+          <t>915; 8024</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3017</t>
+          <t>0; 3113</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22711</t>
+          <t>27579</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4484; 14136</t>
+          <t>4492; 14910</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6173; 18557</t>
+          <t>6287; 19299</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5778; 18392</t>
+          <t>5647; 18297</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9372; 21865</t>
+          <t>11824; 25634</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4570; 14833</t>
+          <t>4076; 14980</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14419; 30731</t>
+          <t>14137; 30575</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9300; 23282</t>
+          <t>9792; 23513</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4774; 12445</t>
+          <t>5816; 14826</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11181; 26193</t>
+          <t>10902; 25698</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24158; 44475</t>
+          <t>23894; 44613</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19332; 38315</t>
+          <t>19221; 37717</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16318; 31240</t>
+          <t>20079; 36990</t>
         </is>
       </c>
     </row>
